--- a/besiktningar/2026/Caravan_Club_Mista_Camping_2026-06-06.xlsx
+++ b/besiktningar/2026/Caravan_Club_Mista_Camping_2026-06-06.xlsx
@@ -429,7 +429,7 @@
         <v>Ansvarig för besiktningen</v>
       </c>
       <c r="B5" t="str">
-        <v>Hans Östman</v>
+        <v>Stefan Leijon</v>
       </c>
     </row>
     <row r="6">
